--- a/resultados/ubirata/inventario_links.xlsx
+++ b/resultados/ubirata/inventario_links.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 18:58:42</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:57</t>
+          <t>2026-08-04 19:00:06</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:59</t>
+          <t>2026-08-04 19:00:09</t>
         </is>
       </c>
     </row>
@@ -600,24 +600,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-001-2024.pdf</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia-api/api/files/arquivo/69582</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>www.ubirata.pr.gov.br</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Instrucao Normativa n 001-2024</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://www.ubirata.pr.gov.br/secretarias/educacao-e-cultura/</t>
-        </is>
-      </c>
+          <t>ubirata.oxy.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>.pdf</t>
@@ -631,7 +623,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:10</t>
+          <t>2026-08-04 19:00:15</t>
         </is>
       </c>
     </row>
@@ -643,7 +635,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-002-2024.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-001-2024.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -653,7 +645,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 002-2024</t>
+          <t>Instrucao Normativa n 001-2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -674,7 +666,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:10</t>
+          <t>2026-08-04 19:00:24</t>
         </is>
       </c>
     </row>
@@ -686,7 +678,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-002-2023-de-03-de-abril-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-002-2024.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -696,7 +688,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 002-2023, de 03 de abril de 2023</t>
+          <t>Instruçao Normativa n 002-2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -717,7 +709,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:11</t>
+          <t>2026-08-04 19:00:24</t>
         </is>
       </c>
     </row>
@@ -729,7 +721,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-003-2023-de-11-de-abril-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-002-2023-de-03-de-abril-de-2023.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -739,7 +731,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Instrucao Normativa n 003-2023, de 11 de abril de 2023</t>
+          <t>Instruçao Normativa n 002-2023, de 03 de abril de 2023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -760,7 +752,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:11</t>
+          <t>2026-08-04 19:00:25</t>
         </is>
       </c>
     </row>
@@ -772,7 +764,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-004-2023-de-30-de-junho-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-003-2023-de-11-de-abril-de-2023.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -782,7 +774,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Instrucao Normativa n 004-2023, de 30 de junho de 2023</t>
+          <t>Instrucao Normativa n 003-2023, de 11 de abril de 2023</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -803,7 +795,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:12</t>
+          <t>2026-08-04 19:00:25</t>
         </is>
       </c>
     </row>
@@ -815,7 +807,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-007-02-de-outubro-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-004-2023-de-30-de-junho-de-2023.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -825,7 +817,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 007, 02 de outubro de 2023</t>
+          <t>Instrucao Normativa n 004-2023, de 30 de junho de 2023</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -846,7 +838,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:12</t>
+          <t>2026-08-04 19:00:26</t>
         </is>
       </c>
     </row>
@@ -858,7 +850,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n.-001-2023-de-06-de-fevereiro-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-007-02-de-outubro-de-2023.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -868,7 +860,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n. 001-2023, de 06 de fevereiro de 2023</t>
+          <t>Instruçao Normativa n 007, 02 de outubro de 2023</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -889,7 +881,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:12</t>
+          <t>2026-08-04 19:00:26</t>
         </is>
       </c>
     </row>
@@ -901,7 +893,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-006-04-de-outubro-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n.-001-2023-de-06-de-fevereiro-de-2023.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -911,7 +903,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Instrução Normativa nº 006, 04 de outubro de 2023</t>
+          <t>Instruçao Normativa n. 001-2023, de 06 de fevereiro de 2023</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -932,7 +924,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:13</t>
+          <t>2026-08-04 19:00:26</t>
         </is>
       </c>
     </row>
@@ -944,7 +936,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-008-03-de-outubro-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-006-04-de-outubro-de-2023.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Instrução Normativa nº 008, 03 de outubro de 2023</t>
+          <t>Instrução Normativa nº 006, 04 de outubro de 2023</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -975,7 +967,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:13</t>
+          <t>2026-08-04 19:00:27</t>
         </is>
       </c>
     </row>
@@ -987,7 +979,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/INSTRUCAO-NORMATIVA-No-009-2023-DE-04-DE-DEZEMBRO-DE-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-008-03-de-outubro-de-2023.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -997,7 +989,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INSTRUÇÃO NORMATIVA Nº 009-2023, DE 04 DE DEZEMBRO DE 2023</t>
+          <t>Instrução Normativa nº 008, 03 de outubro de 2023</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1018,7 +1010,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:14</t>
+          <t>2026-08-04 19:00:27</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1022,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/INSTRUCAO-NORMATIVA-No-010-DE-05-DE-DEZEMBRO-DE-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/INSTRUCAO-NORMATIVA-No-009-2023-DE-04-DE-DEZEMBRO-DE-2023.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1040,7 +1032,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>INSTRUÇÃO NORMATIVA Nº 010, DE 05 DE DEZEMBRO DE 2023</t>
+          <t>INSTRUÇÃO NORMATIVA Nº 009-2023, DE 04 DE DEZEMBRO DE 2023</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1061,7 +1053,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:14</t>
+          <t>2026-08-04 19:00:28</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1065,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no005-2023-de-12-de-setembro-de-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/INSTRUCAO-NORMATIVA-No-010-DE-05-DE-DEZEMBRO-DE-2023.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1083,7 +1075,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Instrução Normativa nº005-2023, de 12 de setembro de 2023</t>
+          <t>INSTRUÇÃO NORMATIVA Nº 010, DE 05 DE DEZEMBRO DE 2023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1104,7 +1096,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:14</t>
+          <t>2026-08-04 19:00:28</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1108,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-Classificacao-Professor-Regente-Professor-de-Ingles-e-Professor-de-Educacao-Fisica.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no005-2023-de-12-de-setembro-de-2023.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1126,7 +1118,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anexo Classificação - Professor Regente, Professor de Inglês e Professor de Educação Física</t>
+          <t>Instrução Normativa nº005-2023, de 12 de setembro de 2023</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1147,7 +1139,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:15</t>
+          <t>2026-08-04 19:00:28</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1151,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CLASSIFICACAO-DE-PROFESSORES-PARA-OFERTA-DE-JORNADA-EM-REGIME-SUPLEMENTAR-DEZEMBRO-DE-2023.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-Classificacao-Professor-Regente-Professor-de-Ingles-e-Professor-de-Educacao-Fisica.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1169,7 +1161,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇAO DE PROFESSORES PARA OFERTA DE JORNADA EM REGIME SUPLEMENTAR DEZEMBRO DE 2023</t>
+          <t>Anexo Classificação - Professor Regente, Professor de Inglês e Professor de Educação Física</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1190,7 +1182,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:15</t>
+          <t>2026-08-04 19:00:29</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1194,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-007-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CLASSIFICACAO-DE-PROFESSORES-PARA-OFERTA-DE-JORNADA-EM-REGIME-SUPLEMENTAR-DEZEMBRO-DE-2023.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1212,7 +1204,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 007-2022</t>
+          <t>CLASSIFICAÇAO DE PROFESSORES PARA OFERTA DE JORNADA EM REGIME SUPLEMENTAR DEZEMBRO DE 2023</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1233,7 +1225,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:16</t>
+          <t>2026-08-04 19:00:29</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1237,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-008-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-007-2022.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1255,7 +1247,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 008-2022</t>
+          <t>Instruçao Normativa n 007-2022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1276,7 +1268,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:16</t>
+          <t>2026-08-04 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1280,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-009-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-008-2022.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1298,7 +1290,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 009-2022</t>
+          <t>Instruçao Normativa n 008-2022</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1319,7 +1311,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:17</t>
+          <t>2026-08-04 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1323,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-010-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-009-2022.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1341,7 +1333,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 010-2022</t>
+          <t>Instruçao Normativa n 009-2022</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1362,7 +1354,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:17</t>
+          <t>2026-08-04 19:00:31</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1366,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-011-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-010-2022.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1384,7 +1376,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 011-2022</t>
+          <t>Instruçao Normativa n 010-2022</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1405,7 +1397,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:17</t>
+          <t>2026-08-04 19:00:31</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1409,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-012-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-011-2022.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1427,7 +1419,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n 012-2022</t>
+          <t>Instruçao Normativa n 011-2022</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1448,7 +1440,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:18</t>
+          <t>2026-08-04 19:00:31</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1452,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n.-015-2022-de-08-de-dezembro-de-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n-012-2022.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1470,7 +1462,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Instruçao Normativa n. 015-2022, de 08 de dezembro de 2022</t>
+          <t>Instruçao Normativa n 012-2022</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1491,7 +1483,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:18</t>
+          <t>2026-08-04 19:00:32</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1495,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-013-DE-21-de-novembro-de-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-n.-015-2022-de-08-de-dezembro-de-2022.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1513,7 +1505,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Instrução Normativa nº 013, DE 21 de novembro de 2022</t>
+          <t>Instruçao Normativa n. 015-2022, de 08 de dezembro de 2022</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1534,7 +1526,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:19</t>
+          <t>2026-08-04 19:00:32</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1538,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no.-014-2022-de-28-de-novembro-de-2022.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no-013-DE-21-de-novembro-de-2022.pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1556,7 +1548,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Instrução Normativa nº. 014-2022, de 28 de novembro de 2022</t>
+          <t>Instrução Normativa nº 013, DE 21 de novembro de 2022</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1577,7 +1569,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:19</t>
+          <t>2026-08-04 19:00:33</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1581,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Classificacao-Professor-Regente-Professor-de-Ingles-e-Professor-de-Educacao-Fisica.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Instrucao-Normativa-no.-014-2022-de-28-de-novembro-de-2022.pdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1599,7 +1591,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Classificação - Professor Regente, Professor de Inglês e Professor de Educação Física</t>
+          <t>Instrução Normativa nº. 014-2022, de 28 de novembro de 2022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1620,7 +1612,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:20</t>
+          <t>2026-08-04 19:00:33</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1624,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-112-2019.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Classificacao-Professor-Regente-Professor-de-Ingles-e-Professor-de-Educacao-Fisica.pdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1642,7 +1634,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Decreto 112-2019</t>
+          <t>Classificação - Professor Regente, Professor de Inglês e Professor de Educação Física</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1663,7 +1655,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:20</t>
+          <t>2026-08-04 19:00:33</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1667,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-no-134-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-112-2019.pdf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1685,7 +1677,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Decreto nº 134-2020</t>
+          <t>Decreto 112-2019</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1706,7 +1698,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:21</t>
+          <t>2026-08-04 19:00:34</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1710,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Homologacao-Participantes-FEMUB-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-no-134-2020.pdf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1728,7 +1720,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Homologação Participantes FEMUB 2020</t>
+          <t>Decreto nº 134-2020</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1749,7 +1741,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:21</t>
+          <t>2026-08-04 19:00:34</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1753,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Portaria-no-1192017.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Homologacao-Participantes-FEMUB-2020.pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1771,7 +1763,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Portaria nº 1192017</t>
+          <t>Homologação Participantes FEMUB 2020</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1792,7 +1784,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:21</t>
+          <t>2026-08-04 19:00:35</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1796,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Ato-no-1-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Portaria-no-1192017.pdf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1814,7 +1806,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ato nº 1-2020</t>
+          <t>Portaria nº 1192017</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1835,7 +1827,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:22</t>
+          <t>2026-08-04 19:00:35</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1839,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-no-67-2020-Nomeia-representante-do-Conselho-do-Fundeb.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Ato-no-1-2020.pdf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1857,7 +1849,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Decreto nº 67-2020 - Nomeia representante do Conselho do Fundeb</t>
+          <t>Ato nº 1-2020</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1878,7 +1870,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:22</t>
+          <t>2026-08-04 19:00:36</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1882,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-I-Decreto-no-84-2020-Classificacao-de-professores-para-oferta-de-jornada-em-regime-suplementar.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-no-67-2020-Nomeia-representante-do-Conselho-do-Fundeb.pdf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1900,7 +1892,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Anexo I - Decreto nº 84-2020 - Classificação de professores para oferta de jornada em regime suplementar</t>
+          <t>Decreto nº 67-2020 - Nomeia representante do Conselho do Fundeb</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1921,7 +1913,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:23</t>
+          <t>2026-08-04 19:00:36</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1925,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-III-Decreto-no-84-2020-Classificacao-de-professores-para-oferta-de-jornada-em-regime-suplementar-Ingles.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-I-Decreto-no-84-2020-Classificacao-de-professores-para-oferta-de-jornada-em-regime-suplementar.pdf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1943,7 +1935,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Anexo III - Decreto nº 84-2020 - Classificação de professores para oferta de jornada em regime suplementar - Inglês</t>
+          <t>Anexo I - Decreto nº 84-2020 - Classificação de professores para oferta de jornada em regime suplementar</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1964,7 +1956,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:23</t>
+          <t>2026-08-04 19:00:36</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1968,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-84-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Anexo-III-Decreto-no-84-2020-Classificacao-de-professores-para-oferta-de-jornada-em-regime-suplementar-Ingles.pdf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1986,7 +1978,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Decreto 84-2020</t>
+          <t>Anexo III - Decreto nº 84-2020 - Classificação de professores para oferta de jornada em regime suplementar - Inglês</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2007,7 +1999,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:24</t>
+          <t>2026-08-04 19:00:37</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2011,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RECOMENDACAO-DO-MP-CARNAVAL-DA-SERINGUEIRA-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-84-2020.pdf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2029,12 +2021,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO DO MP - CARNAVAL DA SERINGUEIRA 2020</t>
+          <t>Decreto 84-2020</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/secretarias/gabinete-do-prefeito/</t>
+          <t>https://www.ubirata.pr.gov.br/secretarias/educacao-e-cultura/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:27</t>
+          <t>2026-08-04 19:00:37</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2054,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/7a-EDICAO-DO-PLANO-DE-CONTIGENCIAMENTO-DO-NOVO-CORONAVIRUS-COVID-19-10-07-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RECOMENDACAO-DO-MP-CARNAVAL-DA-SERINGUEIRA-2020.pdf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2072,12 +2064,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7ª EDIÇÃO DO PLANO DE CONTIGÊNCIAMENTO DO NOVO CORONAVÍRUS (COVID-19) - 10-07-2020</t>
+          <t>RECOMENDAÇÃO DO MP - CARNAVAL DA SERINGUEIRA 2020</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/secretarias/saude/</t>
+          <t>https://www.ubirata.pr.gov.br/secretarias/gabinete-do-prefeito/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2093,7 +2085,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:30</t>
+          <t>2026-08-04 19:00:42</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2097,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/17o-BOLETIM-EPIDEMIOLOGICO-08-07-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/7a-EDICAO-DO-PLANO-DE-CONTIGENCIAMENTO-DO-NOVO-CORONAVIRUS-COVID-19-10-07-2020.pdf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2115,7 +2107,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>17º BOLETIM EPIDEMIOLÓGICO - 08-07-2020</t>
+          <t>7ª EDIÇÃO DO PLANO DE CONTIGÊNCIAMENTO DO NOVO CORONAVÍRUS (COVID-19) - 10-07-2020</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2136,7 +2128,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:30</t>
+          <t>2026-08-04 19:00:44</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2140,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/APRESENTACAO-DA-REUNIAO-SOBRE-O-CORONAVIRUS.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/17o-BOLETIM-EPIDEMIOLOGICO-08-07-2020.pdf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2158,7 +2150,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>APRESENTAÇÃO DA REUNIÃO SOBRE O CORONAVÍRUS</t>
+          <t>17º BOLETIM EPIDEMIOLÓGICO - 08-07-2020</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2179,7 +2171,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:30</t>
+          <t>2026-08-04 19:00:45</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2183,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/AVISO-DE-SUSPENSAO-DE-LICITACAO.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/APRESENTACAO-DA-REUNIAO-SOBRE-O-CORONAVIRUS.pdf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2201,7 +2193,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AVISO DE SUSPENSÃO DE LICITAÇÃO</t>
+          <t>APRESENTAÇÃO DA REUNIÃO SOBRE O CORONAVÍRUS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2222,7 +2214,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:31</t>
+          <t>2026-08-04 19:00:45</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2226,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-27-consolidado.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/AVISO-DE-SUSPENSAO-DE-LICITACAO.pdf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2244,7 +2236,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DECRETO 27 - consolidado</t>
+          <t>AVISO DE SUSPENSÃO DE LICITAÇÃO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2265,7 +2257,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:31</t>
+          <t>2026-08-04 19:00:46</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2269,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-28-consolidado.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-27-consolidado.pdf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2287,7 +2279,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DECRETO 28 - consolidado</t>
+          <t>DECRETO 27 - consolidado</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2308,7 +2300,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:32</t>
+          <t>2026-08-04 19:00:46</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2312,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-37-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-28-consolidado.pdf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2330,7 +2322,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DECRETO 37-2020</t>
+          <t>DECRETO 28 - consolidado</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2351,7 +2343,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:32</t>
+          <t>2026-08-04 19:00:46</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2355,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-38-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-37-2020.pdf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2373,7 +2365,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DECRETO 38-2020</t>
+          <t>DECRETO 37-2020</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2394,7 +2386,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:33</t>
+          <t>2026-08-04 19:00:47</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2398,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-51-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-38-2020.pdf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2416,7 +2408,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DECRETO 51-2020</t>
+          <t>DECRETO 38-2020</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2437,7 +2429,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:33</t>
+          <t>2026-08-04 19:00:47</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2441,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-52-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-51-2020.pdf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2459,7 +2451,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DECRETO 52-2020</t>
+          <t>DECRETO 51-2020</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2480,7 +2472,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:33</t>
+          <t>2026-08-04 19:00:48</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2484,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-53-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-52-2020.pdf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2502,7 +2494,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DECRETO 53-2020</t>
+          <t>DECRETO 52-2020</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2523,7 +2515,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:34</t>
+          <t>2026-08-04 19:00:48</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2527,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-54-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-53-2020.pdf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2545,7 +2537,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DECRETO 54-2020</t>
+          <t>DECRETO 53-2020</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2566,7 +2558,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:34</t>
+          <t>2026-08-04 19:00:48</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2570,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-55-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-54-2020.pdf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2588,7 +2580,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DECRETO 55-2020</t>
+          <t>DECRETO 54-2020</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2609,7 +2601,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:35</t>
+          <t>2026-08-04 19:00:49</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2613,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-66-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-55-2020.pdf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2631,7 +2623,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DECRETO 66-2020</t>
+          <t>DECRETO 55-2020</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2652,7 +2644,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:35</t>
+          <t>2026-08-04 19:00:49</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2656,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-67-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-66-2020.pdf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2674,7 +2666,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DECRETO 67-2020</t>
+          <t>DECRETO 66-2020</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2695,7 +2687,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:35</t>
+          <t>2026-08-04 19:00:50</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2699,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-85-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-67-2020.pdf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2717,7 +2709,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DECRETO 85-2020</t>
+          <t>DECRETO 67-2020</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2738,7 +2730,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:36</t>
+          <t>2026-08-04 19:00:50</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2742,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-87-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-85-2020.pdf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2760,7 +2752,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DECRETO 87-2020</t>
+          <t>DECRETO 85-2020</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2781,7 +2773,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:36</t>
+          <t>2026-08-04 19:00:50</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-N°-39-DE-4-DE-MAIO-DE-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-87-2020.pdf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2803,7 +2795,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DECRETO N° 39, DE 4 DE MAIO DE 2020</t>
+          <t>DECRETO 87-2020</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2824,7 +2816,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:37</t>
+          <t>2026-08-04 19:00:51</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2828,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-que-regulamento-o-uso-de-mascara.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DECRETO-N°-39-DE-4-DE-MAIO-DE-2020.pdf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2846,7 +2838,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Decreto que regulamento o uso de máscara</t>
+          <t>DECRETO N° 39, DE 4 DE MAIO DE 2020</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2867,7 +2859,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:37</t>
+          <t>2026-08-04 19:00:51</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2871,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DETERMINACAO-JUDICIAL-FECHAMENTO-DO-COMERCIO.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/Decreto-que-regulamento-o-uso-de-mascara.pdf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2889,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DETERMINAÇÃO JUDICIAL FECHAMENTO DO COMERCIO</t>
+          <t>Decreto que regulamento o uso de máscara</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2910,7 +2902,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:37</t>
+          <t>2026-08-04 19:00:52</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2914,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DOCUMENTO-QUE-DETERMINOU-O-CANCELAMENTO-DOS-JOGOS.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DETERMINACAO-JUDICIAL-FECHAMENTO-DO-COMERCIO.pdf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2932,7 +2924,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DOCUMENTO QUE DETERMINOU O CANCELAMENTO DOS JOGOS</t>
+          <t>DETERMINAÇÃO JUDICIAL FECHAMENTO DO COMERCIO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2953,7 +2945,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:38</t>
+          <t>2026-08-04 19:00:52</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2957,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/GUIA-DE-ISOLAMENTO-DOMICILIAR-26-03-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/DOCUMENTO-QUE-DETERMINOU-O-CANCELAMENTO-DOS-JOGOS.pdf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2975,7 +2967,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GUIA DE ISOLAMENTO DOMICILIAR - 26-03-2020</t>
+          <t>DOCUMENTO QUE DETERMINOU O CANCELAMENTO DOS JOGOS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2996,7 +2988,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:38</t>
+          <t>2026-08-04 19:00:53</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3000,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/LEI-DE-LIMPEZA-DE-TERRENOS-LEI-N.-2511-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/GUIA-DE-ISOLAMENTO-DOMICILIAR-26-03-2020.pdf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LEI DE LIMPEZA DE TERRENOS - LEI N. 2511-2020</t>
+          <t>GUIA DE ISOLAMENTO DOMICILIAR - 26-03-2020</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3039,7 +3031,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:39</t>
+          <t>2026-08-04 19:00:53</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3043,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/OFICIO-No-261.2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/LEI-DE-LIMPEZA-DE-TERRENOS-LEI-N.-2511-2020.pdf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3061,7 +3053,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OFÍCIO Nº 261.2020</t>
+          <t>LEI DE LIMPEZA DE TERRENOS - LEI N. 2511-2020</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3082,7 +3074,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:39</t>
+          <t>2026-08-04 19:00:53</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3086,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PLANO-MUNICIPAL-DE-FISCALIZACAO-E-MEDIDAS-SANITARIAS-sexta-edicao-17-07-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/OFICIO-No-261.2020.pdf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3104,7 +3096,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PLANO MUNICIPAL DE FISCALIZAÇÃO E MEDIDAS SANITÁRIAS - sexta edição - 17-07-2020</t>
+          <t>OFÍCIO Nº 261.2020</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3125,7 +3117,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:40</t>
+          <t>2026-08-04 19:00:54</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3129,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RECOMENDACAO-No-2448.2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PLANO-MUNICIPAL-DE-FISCALIZACAO-E-MEDIDAS-SANITARIAS-sexta-edicao-17-07-2020.pdf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3147,7 +3139,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO Nº 2448.2020</t>
+          <t>PLANO MUNICIPAL DE FISCALIZAÇÃO E MEDIDAS SANITÁRIAS - sexta edição - 17-07-2020</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3168,7 +3160,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:40</t>
+          <t>2026-08-04 19:00:54</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3172,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/TODOS-OS-DECRETOS-VIGENTES-ATE-16-04-2020.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RECOMENDACAO-No-2448.2020.pdf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3190,7 +3182,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TODOS OS DECRETOS VIGENTES ATÉ 16-04-2020</t>
+          <t>RECOMENDAÇÃO Nº 2448.2020</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3211,7 +3203,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:40</t>
+          <t>2026-08-04 19:00:55</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3215,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/APRESENTACAO-DO-PROGRAMA-RECICLAR-E-NATURAL.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/TODOS-OS-DECRETOS-VIGENTES-ATE-16-04-2020.pdf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3233,7 +3225,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>APRESENTAÇÃO DO PROGRAMA RECICLAR É NATURAL</t>
+          <t>TODOS OS DECRETOS VIGENTES ATÉ 16-04-2020</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3254,7 +3246,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:41</t>
+          <t>2026-08-04 19:00:55</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3258,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PLANO-MUNICIPAL-DE-SAUDE-2019.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/APRESENTACAO-DO-PROGRAMA-RECICLAR-E-NATURAL.pdf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3276,7 +3268,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PLANO MUNICIPAL DE SAÚDE 2019</t>
+          <t>APRESENTAÇÃO DO PROGRAMA RECICLAR É NATURAL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3297,7 +3289,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:41</t>
+          <t>2026-08-04 19:00:55</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3301,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADOS-DA-PROGRAMACAO-2018.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PLANO-MUNICIPAL-DE-SAUDE-2019.pdf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3319,7 +3311,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RESULTADOS DA PROGRAMAÇÃO 2018</t>
+          <t>PLANO MUNICIPAL DE SAÚDE 2019</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3340,7 +3332,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:42</t>
+          <t>2026-08-04 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3344,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PROTOCOLO-PARA-UTILIZACAO-DOS-SERVICOS-DE-TRANSPORTE-PUBLICO-SANITARIO-DA-SECRETARIA-DA-SAUDE-DO-MUNICIPIO-DE-UBIRATA-PR.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADOS-DA-PROGRAMACAO-2018.pdf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3362,7 +3354,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PROTOCOLO PARA UTILIZAÇÃO DOS SERVIÇOS DE TRANSPORTE PÚBLICO SANITÁRIO DA SECRETARIA DA SAÚDE DO MUNICÍPIO DE UBIRATÃ-PR</t>
+          <t>RESULTADOS DA PROGRAMAÇÃO 2018</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3383,7 +3375,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:42</t>
+          <t>2026-08-04 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3387,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/04/Lei-3066-2026.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/PROTOCOLO-PARA-UTILIZACAO-DOS-SERVICOS-DE-TRANSPORTE-PUBLICO-SANITARIO-DA-SECRETARIA-DA-SAUDE-DO-MUNICIPIO-DE-UBIRATA-PR.pdf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3405,12 +3397,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lei 3066-2026</t>
+          <t>PROTOCOLO PARA UTILIZAÇÃO DOS SERVIÇOS DE TRANSPORTE PÚBLICO SANITÁRIO DA SECRETARIA DA SAÚDE DO MUNICÍPIO DE UBIRATÃ-PR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/sim-servico-de-inspecao-municipal/</t>
+          <t>https://www.ubirata.pr.gov.br/secretarias/saude/</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3419,14 +3411,14 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
         <v>200</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:56</t>
+          <t>2026-08-04 19:00:57</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3430,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-1-Gestao-de-Documentos.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/04/Lei-3066-2026.pdf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3448,7 +3440,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Anexo 1 – Gestão de Documentos</t>
+          <t>Lei 3066-2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3458,7 +3450,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>.docx</t>
+          <t>.pdf</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3469,7 +3461,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:57</t>
+          <t>2026-08-04 19:03:51</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3473,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-2-Registro-de-estabelecimento.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-1-Gestao-de-Documentos.docx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3491,7 +3483,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Anexo 2 – Registro de estabelecimento</t>
+          <t>Anexo 1 – Gestão de Documentos</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3512,7 +3504,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:57</t>
+          <t>2026-08-04 19:03:51</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3516,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-3-Registro-de-produtos.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-2-Registro-de-estabelecimento.docx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3534,7 +3526,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Anexo 3 – Registro de produtos</t>
+          <t>Anexo 2 – Registro de estabelecimento</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3555,7 +3547,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:57</t>
+          <t>2026-08-04 19:03:51</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3559,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-4-Coletas-Fiscais.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-3-Registro-de-produtos.docx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3577,7 +3569,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Anexo 4 – Coletas Fiscais</t>
+          <t>Anexo 3 – Registro de produtos</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3598,7 +3590,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:58</t>
+          <t>2026-08-04 19:03:52</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3602,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-5-Combate-a-fraudes.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-4-Coletas-Fiscais.docx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3620,7 +3612,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Anexo 5 – Combate a fraudes</t>
+          <t>Anexo 4 – Coletas Fiscais</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3641,7 +3633,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:58</t>
+          <t>2026-08-04 19:03:52</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3645,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-6-Programas-de-Autocontrole.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-5-Combate-a-fraudes.docx</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3663,7 +3655,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Anexo 6 – Programas de Autocontrole</t>
+          <t>Anexo 5 – Combate a fraudes</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3684,7 +3676,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:59</t>
+          <t>2026-08-04 19:03:53</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3688,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-7-Processos-Administrativos.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-6-Programas-de-Autocontrole.docx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Anexo 7 – Processos Administrativos</t>
+          <t>Anexo 6 – Programas de Autocontrole</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3727,7 +3719,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-08-04 00:16:59</t>
+          <t>2026-08-04 19:03:53</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3731,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-8-Educacao-Sanitaria-e-Clandestinidade.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-7-Processos-Administrativos.docx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3749,7 +3741,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Anexo 8 – Educação Sanitária e Clandestinidade</t>
+          <t>Anexo 7 – Processos Administrativos</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3770,7 +3762,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:00</t>
+          <t>2026-08-04 19:03:53</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3774,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-9-Fiscalizacao.docx</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-8-Educacao-Sanitaria-e-Clandestinidade.docx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3792,7 +3784,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Anexo 9 – Fiscalização</t>
+          <t>Anexo 8 – Educação Sanitária e Clandestinidade</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3813,7 +3805,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:00</t>
+          <t>2026-08-04 19:03:54</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3817,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Decreto-45-2026-publicado.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Anexo-9-Fiscalizacao.docx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3835,7 +3827,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Decreto 45-2026 publicado</t>
+          <t>Anexo 9 – Fiscalização</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3845,7 +3837,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>.pdf</t>
+          <t>.docx</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3856,7 +3848,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:00</t>
+          <t>2026-08-04 19:03:54</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3860,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/02/1.-Edital-Processo-Seletivo-Simplificado-1-2026-1.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/05/Decreto-45-2026-publicado.pdf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3878,12 +3870,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Edital Processo Seletivo Simplificado 1-2026</t>
+          <t>Decreto 45-2026 publicado</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/estao-abertas-as-inscricoes-para-processo-seletivo-simplificado-01-2026/</t>
+          <t>https://www.ubirata.pr.gov.br/sim-servico-de-inspecao-municipal/</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3892,14 +3884,14 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>200</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-08-04 00:18:08</t>
+          <t>2026-08-04 19:03:55</t>
         </is>
       </c>
     </row>
@@ -3911,38 +3903,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/08/Decreto-114-2025.pdf</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia-api/api/files/arquivo/24991</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>www.ubirata.pr.gov.br</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>PLANO MUNICIPAL DE SEGURANÇA ALIMENTAR E NUTRICIONAL DO MUNICÍPIO DE UBIRATÃ 2024 – 2028</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://www.ubirata.pr.gov.br/municipio-de-ubirata-oficializa-plano-municipal-de-seguranca-alimentar-e-nutricional-2024-2028-no-ambito-do-sisan/</t>
-        </is>
-      </c>
+          <t>ubirata.oxy.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>.pdf</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-08-04 00:19:55</t>
+          <t>2026-08-04 19:30:36</t>
         </is>
       </c>
     </row>
@@ -3954,38 +3938,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>http://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/historia_memoria.pdf</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia-api/api/files/arquivo/25234</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>www.ubirata.pr.gov.br</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Livro Ubiratã História e Memória</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>http://www.ubirata.pr.gov.br/</t>
-        </is>
-      </c>
+          <t>ubirata.oxy.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>.pdf</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H83" t="n">
         <v>200</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-08-04 00:20:38</t>
+          <t>2026-08-04 19:30:48</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3973,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/ATA-DE-RESULTADO-FINAL-EDITAL-003-2024.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2026/02/1.-Edital-Processo-Seletivo-Simplificado-1-2026-1.pdf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4007,12 +3983,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ATA DE RESULTADO FINAL – EDITAL 003-2024</t>
+          <t>Edital Processo Seletivo Simplificado 1-2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+          <t>https://www.ubirata.pr.gov.br/estao-abertas-as-inscricoes-para-processo-seletivo-simplificado-01-2026/</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4021,14 +3997,14 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H84" t="n">
         <v>200</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:52</t>
+          <t>2026-08-04 19:51:29</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4016,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADO-FINAL.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/08/Decreto-114-2025.pdf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4050,12 +4026,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RESULTADO FINAL</t>
+          <t>PLANO MUNICIPAL DE SEGURANÇA ALIMENTAR E NUTRICIONAL DO MUNICÍPIO DE UBIRATÃ 2024 – 2028</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+          <t>https://www.ubirata.pr.gov.br/municipio-de-ubirata-oficializa-plano-municipal-de-seguranca-alimentar-e-nutricional-2024-2028-no-ambito-do-sisan/</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4064,14 +4040,14 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:53</t>
+          <t>2026-08-04 20:11:28</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4059,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADO-PRELIMINAR.pdf</t>
+          <t>http://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/historia_memoria.pdf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4093,12 +4069,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RESULTADO PRELIMINAR</t>
+          <t>Livro Ubiratã História e Memória</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+          <t>http://www.ubirata.pr.gov.br/</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4107,14 +4083,14 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:53</t>
+          <t>2026-08-04 20:12:01</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4102,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/AVISO-DE-PRORROGACAO-CHAMAMENTO-PUBLICO-N-003-2024.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/ATA-DE-RESULTADO-FINAL-EDITAL-003-2024.pdf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4136,7 +4112,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AVISO DE PRORROGACAO – CHAMAMENTO PUBLICO N 003-2024</t>
+          <t>ATA DE RESULTADO FINAL – EDITAL 003-2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4157,7 +4133,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:54</t>
+          <t>2026-08-04 20:14:43</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4145,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-003-2024-SELECAO-DE-AGENTES-CULTURAIS-ARTES-CENICAS-ARTES-PLASTICAS-E-DANCA.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADO-FINAL.pdf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4179,7 +4155,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO 003-2024 – SELECAO DE AGENTES CULTURAIS ARTES CENICAS, ARTES PLASTICAS E DANCA</t>
+          <t>RESULTADO FINAL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4200,7 +4176,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:54</t>
+          <t>2026-08-04 20:14:44</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4188,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-002-2024-SELECAO-DE-PROJETOS-CULTURAIS-DOCUMENTARIO.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/RESULTADO-PRELIMINAR.pdf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4222,7 +4198,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO 002-2024 – SELECAO DE PROJETOS CULTURAIS DOCUMENTARIO</t>
+          <t>RESULTADO PRELIMINAR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4243,7 +4219,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:54</t>
+          <t>2026-08-04 20:14:44</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4231,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-001-2024-SELECAO-DE-PROJETOS-CULTURAIS-AUDIOVISUAL.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/AVISO-DE-PRORROGACAO-CHAMAMENTO-PUBLICO-N-003-2024.pdf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4265,7 +4241,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO 001-2024 – SELECAO DE PROJETOS CULTURAIS AUDIOVISUAL</t>
+          <t>AVISO DE PRORROGACAO – CHAMAMENTO PUBLICO N 003-2024</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4286,7 +4262,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:55</t>
+          <t>2026-08-04 20:14:45</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4274,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-4-2023-EDITAL-DE-PREMIACAO-PARA-AGENTES-CULTURAIS-COM-RECURSOS-DA-LEI-COMPLEMENTAR-N-195-2022-LEI-PAULO-GUSTAVO-AUDIOVISUAL.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-003-2024-SELECAO-DE-AGENTES-CULTURAIS-ARTES-CENICAS-ARTES-PLASTICAS-E-DANCA.pdf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4308,7 +4284,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO N 4-2023 – EDITAL DE PREMIACAO PARA AGENTES CULTURAIS COM RECURSOS DA LEI COMPLEMENTAR N 195-2022 (LEI PAULO GUSTAVO) – AUDIOVISUAL</t>
+          <t>CHAMAMENTO PUBLICO 003-2024 – SELECAO DE AGENTES CULTURAIS ARTES CENICAS, ARTES PLASTICAS E DANCA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4329,7 +4305,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:55</t>
+          <t>2026-08-04 20:14:45</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4317,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-0032023-SELECAO-DE-PROJETOS-PARA-FIRMAR-TERMO-DE-EXECUCAO-CULTURAL-COM-RECURSOS-DA-LEI-COMPLEMENTAR-1952022-LEI-PAULO-GUSTAVO-DEMAIS-AREAS-CULTURAIS.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-002-2024-SELECAO-DE-PROJETOS-CULTURAIS-DOCUMENTARIO.pdf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4351,7 +4327,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO N 0032023 – SELECAO DE PROJETOS PARA FIRMAR TERMO DE EXECUCAO CULTURAL COM RECURSOS DA LEI COMPLEMENTAR 1952022 (LEI PAULO GUSTAVO) – DEMAIS AREAS CULTURAIS</t>
+          <t>CHAMAMENTO PUBLICO 002-2024 – SELECAO DE PROJETOS CULTURAIS DOCUMENTARIO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4372,7 +4348,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:56</t>
+          <t>2026-08-04 20:14:45</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4360,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-0022023-PREMIACAO-PARA-AGENTES-CULTURAIS-COM-RECURSOS-DA-LEI-COMPLEMENTAR-N-1952022-LEI-PAULO-GUSTAVO-AUDIOVISUAL.pdf</t>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-001-2024-SELECAO-DE-PROJETOS-CULTURAIS-AUDIOVISUAL.pdf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4394,7 +4370,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO N 0022023 – PREMIACAO PARA AGENTES CULTURAIS COM RECURSOS DA LEI COMPLEMENTAR N 1952022 (LEI PAULO GUSTAVO) – AUDIOVISUAL</t>
+          <t>CHAMAMENTO PUBLICO 001-2024 – SELECAO DE PROJETOS CULTURAIS AUDIOVISUAL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4415,7 +4391,136 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:56</t>
+          <t>2026-08-04 20:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-4-2023-EDITAL-DE-PREMIACAO-PARA-AGENTES-CULTURAIS-COM-RECURSOS-DA-LEI-COMPLEMENTAR-N-195-2022-LEI-PAULO-GUSTAVO-AUDIOVISUAL.pdf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>www.ubirata.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CHAMAMENTO PUBLICO N 4-2023 – EDITAL DE PREMIACAO PARA AGENTES CULTURAIS COM RECURSOS DA LEI COMPLEMENTAR N 195-2022 (LEI PAULO GUSTAVO) – AUDIOVISUAL</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>200</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-0032023-SELECAO-DE-PROJETOS-PARA-FIRMAR-TERMO-DE-EXECUCAO-CULTURAL-COM-RECURSOS-DA-LEI-COMPLEMENTAR-1952022-LEI-PAULO-GUSTAVO-DEMAIS-AREAS-CULTURAIS.pdf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>www.ubirata.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CHAMAMENTO PUBLICO N 0032023 – SELECAO DE PROJETOS PARA FIRMAR TERMO DE EXECUCAO CULTURAL COM RECURSOS DA LEI COMPLEMENTAR 1952022 (LEI PAULO GUSTAVO) – DEMAIS AREAS CULTURAIS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>8</v>
+      </c>
+      <c r="H95" t="n">
+        <v>200</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/wp-content/uploads/2025/04/CHAMAMENTO-PUBLICO-N-0022023-PREMIACAO-PARA-AGENTES-CULTURAIS-COM-RECURSOS-DA-LEI-COMPLEMENTAR-N-1952022-LEI-PAULO-GUSTAVO-AUDIOVISUAL.pdf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>www.ubirata.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CHAMAMENTO PUBLICO N 0022023 – PREMIACAO PARA AGENTES CULTURAIS COM RECURSOS DA LEI COMPLEMENTAR N 1952022 (LEI PAULO GUSTAVO) – AUDIOVISUAL</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/lei-paulo-gustavo/</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>200</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:14:47</t>
         </is>
       </c>
     </row>
